--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search Trends Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="baby skincare" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="babycare" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mitti attar" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pickleball" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -49,9 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -126,6 +132,262 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="26"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1500" b="1" cap="all">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>BABYCARE SEARCH GROWTH TREND</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'babycare'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'babycare'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'babycare'!$D$2:$D$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:srgbClr val="1F1F1F"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="26"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1500" b="1" cap="all">
+                <a:solidFill>
+                  <a:srgbClr val="FFFFFF"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>MITTI ATTAR SEARCH GROWTH TREND</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'mitti attar'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'mitti attar'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'mitti attar'!$D$2:$D$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:srgbClr val="1F1F1F"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,18 +679,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,40 +696,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Pickleball</t>
+          <t>Search Index</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ZBLL</t>
+          <t>Trailing Average</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>baby skincare</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>babycare</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>mitti attar</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Combined Index</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Trailing Average</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Rolling Growth %</t>
         </is>
@@ -484,21 +716,11 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <f>SUM(B2:F2)</f>
-        <v/>
-      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -506,45 +728,295 @@
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3" t="n">
         <v>9.9</v>
       </c>
-      <c r="E3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G3">
-        <f>SUM(B3:F3)</f>
-        <v/>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Search Index</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trailing Average</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rolling Growth %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="C3">
+        <f>AVERAGE(B2:B3)</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C4">
+        <f>AVERAGE(B3:B4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="2">
+        <f>IF(C2=0,"",(C4-C2)/C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>2026-07-27</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="C5">
+        <f>AVERAGE(B4:B5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="2">
+        <f>IF(C3=0,"",(C5-C3)/C3)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Search Index</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trailing Average</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rolling Growth %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C3">
+        <f>AVERAGE(B2:B3)</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <f>AVERAGE(B3:B4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="2">
+        <f>IF(C2=0,"",(C4-C2)/C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="C5">
+        <f>AVERAGE(B4:B5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="2">
+        <f>IF(C3=0,"",(C5-C3)/C3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C6">
+        <f>AVERAGE(B5:B6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="2">
+        <f>IF(C4=0,"",(C6-C4)/C4)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Search Index</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trailing Average</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rolling Growth %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>47.9</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G4">
-        <f>SUM(B4:F4)</f>
-        <v/>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -128,6 +128,152 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="26"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Bodywash - Search Index Over Time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'bodywash'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'bodywash'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'bodywash'!$B$2:$B$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Search Index</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -417,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +604,18 @@
         <v>58</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -173,12 +173,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$3</f>
+              <f>'bodywash'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$3</f>
+              <f>'bodywash'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -614,6 +614,16 @@
         <v>66.7</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>68.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -173,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$4</f>
+              <f>'bodywash'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$4</f>
+              <f>'bodywash'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -563,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -613,6 +616,10 @@
       <c r="B3" t="n">
         <v>66.7</v>
       </c>
+      <c r="C3">
+        <f>AVERAGE(B2:B3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -622,6 +629,32 @@
       </c>
       <c r="B4" t="n">
         <v>68.7</v>
+      </c>
+      <c r="C4">
+        <f>AVERAGE(B3:B4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="2">
+        <f>IF(C2=0,"",(C4-C2)/C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="C5">
+        <f>AVERAGE(B4:B5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="2">
+        <f>IF(C3=0,"",(C5-C3)/C3)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$5</f>
+              <f>'bodywash'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$5</f>
+              <f>'bodywash'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -657,6 +657,24 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="C6">
+        <f>AVERAGE(B5:B6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="2">
+        <f>IF(C4=0,"",(C6-C4)/C4)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$6</f>
+              <f>'bodywash'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$6</f>
+              <f>'bodywash'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -616,10 +616,6 @@
       <c r="B3" t="n">
         <v>66.7</v>
       </c>
-      <c r="C3">
-        <f>AVERAGE(B2:B3)</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -631,11 +627,7 @@
         <v>68.7</v>
       </c>
       <c r="C4">
-        <f>AVERAGE(B3:B4)</f>
-        <v/>
-      </c>
-      <c r="D4" s="2">
-        <f>IF(C2=0,"",(C4-C2)/C2)</f>
+        <f>AVERAGE(B2:B4)</f>
         <v/>
       </c>
     </row>
@@ -649,11 +641,11 @@
         <v>70.40000000000001</v>
       </c>
       <c r="C5">
-        <f>AVERAGE(B4:B5)</f>
+        <f>AVERAGE(B3:B5)</f>
         <v/>
       </c>
       <c r="D5" s="2">
-        <f>IF(C3=0,"",(C5-C3)/C3)</f>
+        <f>IF(C2=0,"",(C5-C2)/C2)</f>
         <v/>
       </c>
     </row>
@@ -667,11 +659,29 @@
         <v>55.3</v>
       </c>
       <c r="C6">
-        <f>AVERAGE(B5:B6)</f>
+        <f>AVERAGE(B4:B6)</f>
         <v/>
       </c>
       <c r="D6" s="2">
-        <f>IF(C4=0,"",(C6-C4)/C4)</f>
+        <f>IF(C3=0,"",(C6-C3)/C3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="C7">
+        <f>AVERAGE(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="2">
+        <f>IF(C4=0,"",(C7-C4)/C4)</f>
         <v/>
       </c>
     </row>

--- a/docs/dashboard.xlsx
+++ b/docs/dashboard.xlsx
@@ -176,12 +176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'bodywash'!$A$2:$A$7</f>
+              <f>'bodywash'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'bodywash'!$B$2:$B$7</f>
+              <f>'bodywash'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -685,6 +685,24 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="C8">
+        <f>AVERAGE(B6:B8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="2">
+        <f>IF(C5=0,"",(C8-C5)/C5)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
